--- a/backend/elderlycare-common/src/main/resources/excel_model/UserManagement.xlsx
+++ b/backend/elderlycare-common/src/main/resources/excel_model/UserManagement.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -454,7 +454,6 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,11 +487,6 @@
           <t>状态</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -525,11 +519,6 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>operation</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -560,11 +549,6 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>编辑/禁用</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -595,11 +579,6 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>编辑/禁用</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -628,11 +607,6 @@
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>正常</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>编辑/禁用</t>
         </is>
       </c>
     </row>
